--- a/posts/demo-sheet-for-loom.xlsx
+++ b/posts/demo-sheet-for-loom.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transacciones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deudas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cashflow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deudas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.00\%"/>
+    <numFmt numFmtId="165" formatCode="0&quot; gandolas&quot;"/>
+    <numFmt numFmtId="166" formatCode="0&quot; cobros&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\%"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,13 +36,24 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D4B88C"/>
-      <sz val="22"/>
+      <color rgb="00C9A961"/>
+      <sz val="14"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="0064748B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="00C9A961"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4D2E"/>
+      <sz val="36"/>
     </font>
     <font>
       <b val="1"/>
@@ -48,17 +62,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D4B88C"/>
-      <sz val="14"/>
+      <color rgb="001F4D2E"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000F172A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="001F4D2E"/>
       <sz val="20"/>
     </font>
     <font>
@@ -68,13 +77,43 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C9A961"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00059669"/>
       <sz val="20"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D4B88C"/>
-      <sz val="12"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="22"/>
     </font>
     <font>
       <b val="1"/>
@@ -92,7 +131,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D4B88C"/>
+      <color rgb="00C9A961"/>
       <sz val="11"/>
     </font>
     <font>
@@ -102,13 +141,26 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C9A961"/>
+      <sz val="18"/>
+    </font>
+    <font>
       <color rgb="00166534"/>
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00991B1B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4D2E"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00991B1B"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -117,7 +169,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000F172A"/>
+      <color rgb="001F4D2E"/>
     </font>
     <font>
       <b val="1"/>
@@ -134,7 +186,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000F172A"/>
+      <color rgb="001F4D2E"/>
       <sz val="16"/>
     </font>
     <font>
@@ -147,7 +199,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -156,7 +208,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
+        <fgColor rgb="001F4D2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5ECD7"/>
       </patternFill>
     </fill>
     <fill>
@@ -186,7 +243,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5ECD7"/>
+        <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -216,130 +273,183 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,6 +524,214 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cashflow diario · Saldo acumulado</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Cashflow'!E5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Cashflow'!$B$6:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cashflow'!$E$6:$E$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Cashflow'!F5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Cashflow'!$B$6:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cashflow'!$F$6:$F$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Fecha</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Monto USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3429000" cy="1028700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -705,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I26"/>
+  <dimension ref="B4:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -719,291 +1037,410 @@
     <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="50" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>GOLDEN OIL DEMO  ·  Repositorio Zelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Demo creado por ZENIA  ·  zeniapartners.com  ·  Datos ficticios</t>
+    <row r="1" ht="38" customHeight="1"/>
+    <row r="2" ht="38" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>REPOSITORIO ZELLE  ·  Mes en curso (Mayo 2026)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Demo creado por ZENIA  ·  zeniapartners.com  ·  Datos ficticios (cliente y operacion inventados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>EFECTIVO TRAZADO TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="B8" s="4">
+        <f>C12+E12+G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Suma trazada: liquido en banco + capital en gandolas + cuentas por cobrar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>SALDO INICIAL BANCO (editable):</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E10" s="7" t="n">
         <v>35000</v>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>TRAZABILIDAD DEL EFECTIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>EFECTIVO EN BANCO</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>DINERO EN GANDOLAS</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>CUENTAS POR COBRAR</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>TOTAL TRAZADO</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="B10" s="10">
-        <f>E5+SUMIFS(Transacciones!D:D,Transacciones!E:E,"in")-SUMIFS(Transacciones!D:D,Transacciones!E:E,"out")-(SUMIFS(Transacciones!D:D,Transacciones!F:F,"entrega_gandola")-SUMIFS(Transacciones!D:D,Transacciones!F:F,"retorno_gandola"))-(SUMIFS(Transacciones!D:D,Transacciones!F:F,"venta_credito")-SUMIFS(Transacciones!D:D,Transacciones!F:F,"cobro_credito"))</f>
-        <v/>
-      </c>
-      <c r="D10" s="11">
+    <row r="12" ht="60" customHeight="1">
+      <c r="B12" s="12">
+        <f>E10+SUMIFS(Transacciones!D:D,Transacciones!E:E,"in")-SUMIFS(Transacciones!D:D,Transacciones!E:E,"out")-(SUMIFS(Transacciones!D:D,Transacciones!F:F,"entrega_gandola")-SUMIFS(Transacciones!D:D,Transacciones!F:F,"retorno_gandola"))-(SUMIFS(Transacciones!D:D,Transacciones!F:F,"venta_credito")-SUMIFS(Transacciones!D:D,Transacciones!F:F,"cobro_credito"))</f>
+        <v/>
+      </c>
+      <c r="D12" s="13">
         <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"entrega_gandola")-SUMIFS(Transacciones!D:D,Transacciones!F:F,"retorno_gandola")</f>
         <v/>
       </c>
-      <c r="F10" s="12">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"venta_credito")-SUMIFS(Transacciones!D:D,Transacciones!F:F,"cobro_credito")+IFERROR(Deudas!I35,0)</f>
-        <v/>
-      </c>
-      <c r="H10" s="13">
-        <f>C10+E10+G10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="F12" s="14">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"venta_credito")-SUMIFS(Transacciones!D:D,Transacciones!F:F,"cobro_credito")</f>
+        <v/>
+      </c>
+      <c r="H12" s="15">
+        <f>C12+E12+G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Saldo liquido</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Capital en transito</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Pendiente de cobrar</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H13" s="19" t="inlineStr">
         <is>
           <t>Suma de los 3</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="5" t="inlineStr">
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>KPIs DEL PERIODO</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="9" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>INGRESOS COBRADOS</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>GASTOS PAGADOS</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>FLUJO NETO</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>TICKET PROMEDIO</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="B16" s="20">
+    <row r="18" ht="60" customHeight="1">
+      <c r="B18" s="23">
         <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in")</f>
         <v/>
       </c>
-      <c r="D16" s="21">
+      <c r="D18" s="24">
         <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out")</f>
         <v/>
       </c>
-      <c r="F16" s="22">
-        <f>C16-E16</f>
-        <v/>
-      </c>
-      <c r="H16" s="23">
-        <f>IFERROR(C16/COUNTIFS(Transacciones!E:E,"in"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="F18" s="25">
+        <f>C18-E18</f>
+        <v/>
+      </c>
+      <c r="H18" s="26">
+        <f>IFERROR(C18/COUNTIFS(Transacciones!E:E,"in"),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Total in</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Total out</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>Cashflow del periodo</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>Por transferencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>TOP 5 PAGADORES</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="27" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>Por cobro</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>ALERTAS Y RESUMEN OPERATIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>!  GANDOLAS ACTIVAS</t>
+        </is>
+      </c>
+      <c r="E23" s="30" t="inlineStr">
+        <is>
+          <t>!  PROXIMO PAGO INTERES</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>+  COBROS ESTA SEMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="50" customHeight="1">
+      <c r="B24" s="32">
+        <f>COUNTIFS(Transacciones!F:F,"entrega_gandola")-COUNTIFS(Transacciones!F:F,"retorno_gandola")</f>
+        <v/>
+      </c>
+      <c r="E24" s="33" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G24" s="34">
+        <f>COUNTIFS(Transacciones!E:E,"in")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Capital en ruta sin cerrar</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>Luis Mendoza · vence 28-MAY</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>Pagos recibidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>TOP PAGADORES DEL PERIODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D28" s="35" t="inlineStr">
         <is>
           <t>Total Cobrado</t>
         </is>
       </c>
-      <c r="F21" s="27" t="inlineStr">
+      <c r="F28" s="35" t="inlineStr">
         <is>
           <t># Pagos</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="28" t="inlineStr">
+      <c r="H28" s="35" t="inlineStr">
+        <is>
+          <t>Ticket Promedio</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>Carlos Perez</t>
+        </is>
+      </c>
+      <c r="D29" s="37" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F29" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="39" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>Empresa XYZ</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F30" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="39" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="36" t="inlineStr">
+        <is>
+          <t>Lucia Ramirez</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F31" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="39" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>Pedro Lopez</t>
+        </is>
+      </c>
+      <c r="D32" s="37" t="n">
+        <v>800</v>
+      </c>
+      <c r="F32" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="39" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>Maria Gonzalez</t>
         </is>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D33" s="37" t="n">
         <v>500</v>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F33" s="38" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>Carlos Perez</t>
-        </is>
-      </c>
-      <c r="D23" s="29" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F23" s="30" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>Empresa XYZ</t>
-        </is>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>850</v>
-      </c>
-      <c r="F24" s="30" t="n">
+      <c r="H33" s="39" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>Restaurante Lima</t>
+        </is>
+      </c>
+      <c r="D34" s="37" t="n">
+        <v>450</v>
+      </c>
+      <c r="F34" s="38" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="28" t="inlineStr">
-        <is>
-          <t>Lucia Ramirez</t>
-        </is>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>650</v>
-      </c>
-      <c r="F25" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="28" t="inlineStr">
-        <is>
-          <t>Pedro Lopez</t>
-        </is>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>400</v>
-      </c>
-      <c r="F26" s="30" t="n">
-        <v>1</v>
+      <c r="H34" s="39" t="n">
+        <v>450</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="42">
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D10:E10"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B21:I21"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F18:G18"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B8:I8"/>
     <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="H17:I17"/>
-    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G25:I25"/>
     <mergeCell ref="H11:I11"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1013,7 +1450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1022,694 +1459,1128 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B1" s="40" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C1" s="31" t="inlineStr">
+      <c r="C1" s="40" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D1" s="31" t="inlineStr">
+      <c r="D1" s="40" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="E1" s="31" t="inlineStr">
+      <c r="E1" s="40" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="F1" s="40" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G1" s="40" t="inlineStr">
         <is>
           <t>Conf#</t>
         </is>
       </c>
-      <c r="H1" s="31" t="inlineStr">
+      <c r="H1" s="40" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="I1" s="31" t="inlineStr">
+      <c r="I1" s="40" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>D-001</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="41" t="inlineStr">
         <is>
           <t>Maria Gonzalez</t>
         </is>
       </c>
-      <c r="D2" s="33" t="n">
+      <c r="D2" s="42" t="n">
         <v>500</v>
       </c>
-      <c r="E2" s="34" t="inlineStr">
+      <c r="E2" s="43" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" s="41" t="inlineStr">
         <is>
           <t>cobro_cliente</t>
         </is>
       </c>
-      <c r="G2" s="32" t="inlineStr">
+      <c r="G2" s="41" t="inlineStr">
         <is>
           <t>ABC123XYZ</t>
         </is>
       </c>
-      <c r="H2" s="32" t="inlineStr">
+      <c r="H2" s="41" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="I2" s="32" t="inlineStr">
-        <is>
-          <t>Pago anticipo orden #1247</t>
+      <c r="I2" s="41" t="inlineStr">
+        <is>
+          <t>Pago anticipo orden #4421</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>D-002</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="44" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="44" t="inlineStr">
         <is>
           <t>Carlos Perez</t>
         </is>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D3" s="45" t="n">
         <v>700</v>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="46" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="44" t="inlineStr">
         <is>
           <t>cobro_cliente</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr">
+      <c r="G3" s="44" t="inlineStr">
         <is>
           <t>XYZ789DEF</t>
         </is>
       </c>
-      <c r="H3" s="32" t="inlineStr">
+      <c r="H3" s="44" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="I3" s="32" t="inlineStr">
-        <is>
-          <t>Pago final pedido</t>
+      <c r="I3" s="44" t="inlineStr">
+        <is>
+          <t>Pago final pedido botellas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>D-003</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>Empresa XYZ</t>
         </is>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="42" t="n">
         <v>850</v>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>cobro_cliente</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>QWE456RTY</t>
         </is>
       </c>
-      <c r="H4" s="32" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="I4" s="32" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>Pago factura mayo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>D-004</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Carlos Perez</t>
         </is>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="45" t="n">
         <v>500</v>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>cobro_cliente</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>MNB789POI</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>Anticipo pedido grande</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>D-005</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>Lucia Ramirez</t>
         </is>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="42" t="n">
         <v>650</v>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="43" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="41" t="inlineStr">
         <is>
           <t>cobro_cliente</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" s="41" t="inlineStr">
         <is>
           <t>ZXC123ASD</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="41" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="41" t="inlineStr">
+        <is>
+          <t>Pago semanal restaurante</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>D-006</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>Gandola Beleva</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="47" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F7" s="44" t="inlineStr">
+        <is>
+          <t>entrega_gandola</t>
+        </is>
+      </c>
+      <c r="G7" s="44" t="inlineStr"/>
+      <c r="H7" s="44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I7" s="44" t="inlineStr">
+        <is>
+          <t>Capital viaje Caracas - flete + impuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>D-007</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Pedro Lopez</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>400</v>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
+          <t>cobro_cliente</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>WER567TYU</t>
+        </is>
+      </c>
+      <c r="H8" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I8" s="41" t="inlineStr">
+        <is>
+          <t>Pago tienda esquina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>D-008</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>Juan Rodriguez</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="E9" s="47" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>venta_credito</t>
+        </is>
+      </c>
+      <c r="G9" s="44" t="inlineStr"/>
+      <c r="H9" s="44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I9" s="44" t="inlineStr">
+        <is>
+          <t>Mercancia paga el 15 de mayo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>D-009</t>
+        </is>
+      </c>
+      <c r="B10" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Planilla Equipo</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E10" s="48" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F10" s="41" t="inlineStr">
+        <is>
+          <t>planilla</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr"/>
+      <c r="H10" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I10" s="41" t="inlineStr">
+        <is>
+          <t>Quincena fin abril</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>D-010</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>Aduana DAE</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>impuesto_gandola</t>
+        </is>
+      </c>
+      <c r="G11" s="44" t="inlineStr"/>
+      <c r="H11" s="44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I11" s="44" t="inlineStr">
+        <is>
+          <t>Permiso ingreso Venezuela</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>D-011</t>
+        </is>
+      </c>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>Luis Mendoza</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="48" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F12" s="41" t="inlineStr">
+        <is>
+          <t>pago_deuda_interes</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr"/>
+      <c r="H12" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I12" s="41" t="inlineStr">
+        <is>
+          <t>Interes mensual abril (4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>D-012</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>Pedro Ramos</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E13" s="47" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>pago_deuda_interes</t>
+        </is>
+      </c>
+      <c r="G13" s="44" t="inlineStr"/>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I13" s="44" t="inlineStr">
+        <is>
+          <t>Interes mensual abril (5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>D-013</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Logistica Andes</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E14" s="48" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F14" s="41" t="inlineStr">
+        <is>
+          <t>gasto_logistica</t>
+        </is>
+      </c>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>WT2026050108821</t>
+        </is>
+      </c>
+      <c r="H14" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I14" s="41" t="inlineStr">
+        <is>
+          <t>Flete contenedor #C-2204</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>D-014</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>Gandola Beleva</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E15" s="46" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>retorno_gandola</t>
+        </is>
+      </c>
+      <c r="G15" s="44" t="inlineStr"/>
+      <c r="H15" s="44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I15" s="44" t="inlineStr">
+        <is>
+          <t>Cierre viaje Caracas - efectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>D-015</t>
+        </is>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Viaticos chofer</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="n">
+        <v>320</v>
+      </c>
+      <c r="E16" s="48" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F16" s="41" t="inlineStr">
+        <is>
+          <t>viaticos</t>
+        </is>
+      </c>
+      <c r="G16" s="41" t="inlineStr"/>
+      <c r="H16" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I16" s="41" t="inlineStr">
+        <is>
+          <t>Comida + peajes Caracas</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>D-016</t>
+        </is>
+      </c>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C17" s="44" t="inlineStr">
+        <is>
+          <t>Lucia Ramirez</t>
+        </is>
+      </c>
+      <c r="D17" s="45" t="n">
+        <v>650</v>
+      </c>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F17" s="44" t="inlineStr">
+        <is>
+          <t>cobro_cliente</t>
+        </is>
+      </c>
+      <c r="G17" s="44" t="inlineStr">
+        <is>
+          <t>POI234UYT</t>
+        </is>
+      </c>
+      <c r="H17" s="44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I17" s="44" t="inlineStr">
+        <is>
+          <t>Pago semanal restaurante</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>D-017</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Empresa XYZ</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="n">
+        <v>850</v>
+      </c>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F18" s="41" t="inlineStr">
+        <is>
+          <t>cobro_cliente</t>
+        </is>
+      </c>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>LKJ567HGF</t>
+        </is>
+      </c>
+      <c r="H18" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I18" s="41" t="inlineStr">
+        <is>
+          <t>Pago factura abril</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>D-018</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="inlineStr">
+        <is>
+          <t>Almacen Doral</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="n">
+        <v>780</v>
+      </c>
+      <c r="E19" s="47" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>alquiler</t>
+        </is>
+      </c>
+      <c r="G19" s="44" t="inlineStr"/>
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I19" s="44" t="inlineStr">
+        <is>
+          <t>Renta mayo galpon</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>D-019</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>Pedro Lopez</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="n">
+        <v>400</v>
+      </c>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>cobro_cliente</t>
+        </is>
+      </c>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>MNB456VCX</t>
+        </is>
+      </c>
+      <c r="H20" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I20" s="41" t="inlineStr">
         <is>
           <t>Pago semanal</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>D-006</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>D-020</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>Restaurante Lima</t>
+        </is>
+      </c>
+      <c r="D21" s="45" t="n">
+        <v>450</v>
+      </c>
+      <c r="E21" s="46" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="F21" s="44" t="inlineStr">
+        <is>
+          <t>cobro_cliente</t>
+        </is>
+      </c>
+      <c r="G21" s="44" t="inlineStr">
+        <is>
+          <t>QAZ123WSX</t>
+        </is>
+      </c>
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I21" s="44" t="inlineStr">
+        <is>
+          <t>Pago primera caja</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>D-021</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t>Combustible flota</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="n">
+        <v>240</v>
+      </c>
+      <c r="E22" s="48" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F22" s="41" t="inlineStr">
+        <is>
+          <t>combustible</t>
+        </is>
+      </c>
+      <c r="G22" s="41" t="inlineStr"/>
+      <c r="H22" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I22" s="41" t="inlineStr">
+        <is>
+          <t>Gasolina 2 furgonetas</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>D-022</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="inlineStr">
         <is>
           <t>Gandola Beleva</t>
         </is>
       </c>
-      <c r="D7" s="33" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="D23" s="45" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E23" s="47" t="inlineStr">
         <is>
           <t>out</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F23" s="44" t="inlineStr">
         <is>
           <t>entrega_gandola</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr"/>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="G23" s="44" t="inlineStr"/>
+      <c r="H23" s="44" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="I7" s="32" t="inlineStr">
-        <is>
-          <t>Capital viaje Caracas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>D-007</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>Pedro Lopez</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>400</v>
-      </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="I23" s="44" t="inlineStr">
+        <is>
+          <t>Capital nuevo viaje Maracaibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>D-023</t>
+        </is>
+      </c>
+      <c r="B24" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>Asesoria Contable</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="n">
+        <v>480</v>
+      </c>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F24" s="41" t="inlineStr">
+        <is>
+          <t>honorarios</t>
+        </is>
+      </c>
+      <c r="G24" s="41" t="inlineStr"/>
+      <c r="H24" s="41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I24" s="41" t="inlineStr">
+        <is>
+          <t>Honorarios mensuales</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>D-024</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>Carmona (cliente)</t>
+        </is>
+      </c>
+      <c r="D25" s="45" t="n">
+        <v>650</v>
+      </c>
+      <c r="E25" s="46" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
-        <is>
-          <t>cobro_cliente</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>WER567TYU</t>
-        </is>
-      </c>
-      <c r="H8" s="32" t="inlineStr">
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>cobro_credito</t>
+        </is>
+      </c>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>VBN234ZAQ</t>
+        </is>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>D-008</t>
-        </is>
-      </c>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>Juan Rodriguez</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>800</v>
-      </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="I25" s="44" t="inlineStr">
+        <is>
+          <t>Cancela mercancia entregada el 5 abr</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>D-025</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>Telefonia movil</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="n">
+        <v>85</v>
+      </c>
+      <c r="E26" s="48" t="inlineStr">
         <is>
           <t>out</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>venta_credito</t>
-        </is>
-      </c>
-      <c r="G9" s="32" t="inlineStr"/>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="F26" s="41" t="inlineStr">
+        <is>
+          <t>servicios</t>
+        </is>
+      </c>
+      <c r="G26" s="41" t="inlineStr"/>
+      <c r="H26" s="41" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
-        <is>
-          <t>Mercancia paga el 15 de mayo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>D-009</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="inlineStr">
-        <is>
-          <t>Planilla Equipo</t>
-        </is>
-      </c>
-      <c r="D10" s="33" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E10" s="35" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="F10" s="32" t="inlineStr">
-        <is>
-          <t>planilla</t>
-        </is>
-      </c>
-      <c r="G10" s="32" t="inlineStr"/>
-      <c r="H10" s="32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I10" s="32" t="inlineStr">
-        <is>
-          <t>Quincena fin abril</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>D-010</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>Aduana DAE</t>
-        </is>
-      </c>
-      <c r="D11" s="33" t="n">
-        <v>1350</v>
-      </c>
-      <c r="E11" s="35" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>impuesto_gandola</t>
-        </is>
-      </c>
-      <c r="G11" s="32" t="inlineStr"/>
-      <c r="H11" s="32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I11" s="32" t="inlineStr">
-        <is>
-          <t>Permiso ingreso Venezuela</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>D-011</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>Luis Mendoza</t>
-        </is>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E12" s="35" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>pago_deuda_interes</t>
-        </is>
-      </c>
-      <c r="G12" s="32" t="inlineStr"/>
-      <c r="H12" s="32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I12" s="32" t="inlineStr">
-        <is>
-          <t>Interes mensual abril</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>D-012</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="inlineStr">
-        <is>
-          <t>Pedro Ramos</t>
-        </is>
-      </c>
-      <c r="D13" s="33" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E13" s="35" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="F13" s="32" t="inlineStr">
-        <is>
-          <t>pago_deuda_interes</t>
-        </is>
-      </c>
-      <c r="G13" s="32" t="inlineStr"/>
-      <c r="H13" s="32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I13" s="32" t="inlineStr">
-        <is>
-          <t>Interes mensual abril</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>D-013</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C14" s="32" t="inlineStr">
-        <is>
-          <t>Logistica Andes</t>
-        </is>
-      </c>
-      <c r="D14" s="33" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E14" s="35" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>gasto_logistica</t>
-        </is>
-      </c>
-      <c r="G14" s="32" t="inlineStr"/>
-      <c r="H14" s="32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I14" s="32" t="inlineStr">
-        <is>
-          <t>Flete contenedor</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>D-014</t>
-        </is>
-      </c>
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>Gandola Beleva</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="n">
-        <v>4200</v>
-      </c>
-      <c r="E15" s="34" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>retorno_gandola</t>
-        </is>
-      </c>
-      <c r="G15" s="32" t="inlineStr"/>
-      <c r="H15" s="32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I15" s="32" t="inlineStr">
-        <is>
-          <t>Cierre viaje Caracas - efectivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>D-015</t>
-        </is>
-      </c>
-      <c r="B16" s="32" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C16" s="32" t="inlineStr">
-        <is>
-          <t>Viaticos chofer</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="n">
-        <v>320</v>
-      </c>
-      <c r="E16" s="35" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="F16" s="32" t="inlineStr">
-        <is>
-          <t>viaticos</t>
-        </is>
-      </c>
-      <c r="G16" s="32" t="inlineStr"/>
-      <c r="H16" s="32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I16" s="32" t="inlineStr">
-        <is>
-          <t>Comida + peajes Caracas</t>
+      <c r="I26" s="41" t="inlineStr">
+        <is>
+          <t>Plan business Verizon</t>
         </is>
       </c>
     </row>
@@ -1719,6 +2590,409 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" s="49" t="inlineStr">
+        <is>
+          <t>CASHFLOW DIARIO  ·  Mayo 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Movimientos consolidados por fecha. Ingresos / Gastos / Flujo / Saldo acumulado.</t>
+        </is>
+      </c>
+      <c r="I3" s="50" t="inlineStr">
+        <is>
+          <t>Saldo inicial (Portada!E10):</t>
+        </is>
+      </c>
+      <c r="J3" s="51">
+        <f>Portada!E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="B5" s="52" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="D5" s="52" t="inlineStr">
+        <is>
+          <t>Gastos</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>Flujo Neto</t>
+        </is>
+      </c>
+      <c r="F5" s="52" t="inlineStr">
+        <is>
+          <t>Saldo Acumulado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C6" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-22")</f>
+        <v/>
+      </c>
+      <c r="D6" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-22")</f>
+        <v/>
+      </c>
+      <c r="E6" s="55">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="51">
+        <f>$J$3+E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C7" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-23")</f>
+        <v/>
+      </c>
+      <c r="D7" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-23")</f>
+        <v/>
+      </c>
+      <c r="E7" s="55">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="51">
+        <f>F6+E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C8" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-24")</f>
+        <v/>
+      </c>
+      <c r="D8" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-24")</f>
+        <v/>
+      </c>
+      <c r="E8" s="55">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="51">
+        <f>F7+E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C9" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-25")</f>
+        <v/>
+      </c>
+      <c r="D9" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-25")</f>
+        <v/>
+      </c>
+      <c r="E9" s="55">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="51">
+        <f>F8+E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C10" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-26")</f>
+        <v/>
+      </c>
+      <c r="D10" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-26")</f>
+        <v/>
+      </c>
+      <c r="E10" s="55">
+        <f>Portada!E10</f>
+        <v/>
+      </c>
+      <c r="F10" s="51">
+        <f>F9+E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C11" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-27")</f>
+        <v/>
+      </c>
+      <c r="D11" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-27")</f>
+        <v/>
+      </c>
+      <c r="E11" s="55">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="51">
+        <f>F10+E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C12" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-28")</f>
+        <v/>
+      </c>
+      <c r="D12" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-28")</f>
+        <v/>
+      </c>
+      <c r="E12" s="55">
+        <f>C12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="51">
+        <f>F11+E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C13" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-29")</f>
+        <v/>
+      </c>
+      <c r="D13" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-29")</f>
+        <v/>
+      </c>
+      <c r="E13" s="55">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="51">
+        <f>F12+E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C14" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-30")</f>
+        <v/>
+      </c>
+      <c r="D14" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-30")</f>
+        <v/>
+      </c>
+      <c r="E14" s="55">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="51">
+        <f>F13+E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C15" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-05-01")</f>
+        <v/>
+      </c>
+      <c r="D15" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-05-01")</f>
+        <v/>
+      </c>
+      <c r="E15" s="55">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="51">
+        <f>F14+E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="C16" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-05-02")</f>
+        <v/>
+      </c>
+      <c r="D16" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-05-02")</f>
+        <v/>
+      </c>
+      <c r="E16" s="55">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="51">
+        <f>F15+E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C17" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-05-03")</f>
+        <v/>
+      </c>
+      <c r="D17" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-05-03")</f>
+        <v/>
+      </c>
+      <c r="E17" s="55">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="51">
+        <f>F16+E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C18" s="53">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-05-04")</f>
+        <v/>
+      </c>
+      <c r="D18" s="54">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-05-04")</f>
+        <v/>
+      </c>
+      <c r="E18" s="55">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="51">
+        <f>F17+E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="56" t="inlineStr">
+        <is>
+          <t>TOTAL PERIODO</t>
+        </is>
+      </c>
+      <c r="C19" s="57">
+        <f>SUM(C6:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="58">
+        <f>SUM(D6:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="59">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="60">
+        <f>F18</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1740,254 +3014,254 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DEUDAS  ·  Por cobrar / Por pagar</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Deudor / Acreedor</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Capital Original</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Fecha Inicio</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Tasa Mensual %</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Meses Transc.</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t>Interes Mensual Fijo</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>Pagos a Capital</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Saldo Vivo</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" s="22" t="inlineStr">
         <is>
           <t>Fecha Vcto.</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t>Dias p/Vcto.</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" s="22" t="inlineStr">
         <is>
           <t>Forma de Pago</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" s="22" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>Luis Mendoza</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>Por Pagar</t>
         </is>
       </c>
-      <c r="C4" s="37" t="n">
+      <c r="C4" s="62" t="n">
         <v>40000</v>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="61" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="E4" s="38" t="n">
+      <c r="E4" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="36" t="n">
+      <c r="F4" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="39" t="n">
+      <c r="G4" s="64" t="n">
         <v>1600</v>
       </c>
-      <c r="H4" s="39" t="n">
+      <c r="H4" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="40" t="n">
+      <c r="I4" s="65" t="n">
         <v>40000</v>
       </c>
-      <c r="J4" s="36" t="inlineStr"/>
-      <c r="K4" s="36" t="inlineStr"/>
-      <c r="L4" s="36" t="inlineStr">
+      <c r="J4" s="61" t="inlineStr"/>
+      <c r="K4" s="61" t="inlineStr"/>
+      <c r="L4" s="61" t="inlineStr">
         <is>
           <t>Transferencia mensual</t>
         </is>
       </c>
-      <c r="M4" s="36" t="inlineStr">
+      <c r="M4" s="61" t="inlineStr">
         <is>
           <t>Sin vcto.</t>
         </is>
       </c>
-      <c r="N4" s="36" t="inlineStr">
+      <c r="N4" s="61" t="inlineStr">
         <is>
           <t>Prestamo dic 2025. Capital $40,000. Interes 4% mensual fijo $1,600. Solo se pagan intereses; capital intacto.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>Pedro Ramos</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>Por Pagar</t>
         </is>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="62" t="n">
         <v>50000</v>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="39" t="n">
+      <c r="G5" s="64" t="n">
         <v>2500</v>
       </c>
-      <c r="H5" s="39" t="n">
+      <c r="H5" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="40" t="n">
+      <c r="I5" s="65" t="n">
         <v>50000</v>
       </c>
-      <c r="J5" s="36" t="inlineStr"/>
-      <c r="K5" s="36" t="inlineStr"/>
-      <c r="L5" s="36" t="inlineStr">
+      <c r="J5" s="61" t="inlineStr"/>
+      <c r="K5" s="61" t="inlineStr"/>
+      <c r="L5" s="61" t="inlineStr">
         <is>
           <t>Transferencia mensual</t>
         </is>
       </c>
-      <c r="M5" s="36" t="inlineStr">
+      <c r="M5" s="61" t="inlineStr">
         <is>
           <t>Sin vcto.</t>
         </is>
       </c>
-      <c r="N5" s="36" t="inlineStr">
+      <c r="N5" s="61" t="inlineStr">
         <is>
           <t>Prestamo dic 2025. Capital $50,000. Interes 5% mensual fijo $2,500. Solo se pagan intereses; capital intacto.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>TOTAL POR PAGAR</t>
         </is>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="60" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G10" s="67" t="n">
         <v>4100</v>
       </c>
-      <c r="I10" s="44" t="n">
+      <c r="I10" s="68" t="n">
         <v>90000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>CREDITO ROTATIVO PROVEEDOR</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Cisterna Pendiente</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>Fecha Entrega</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="46" t="inlineStr">
-        <is>
-          <t>Royal Caribena</t>
-        </is>
-      </c>
-      <c r="B16" s="47" t="inlineStr">
-        <is>
-          <t>Cisterna 15 (BS150)</t>
-        </is>
-      </c>
-      <c r="C16" s="48" t="n">
-        <v>65637.82000000001</v>
-      </c>
-      <c r="D16" s="47" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
+      <c r="A16" s="70" t="inlineStr">
+        <is>
+          <t>Olivar Andaluz S.L.</t>
+        </is>
+      </c>
+      <c r="B16" s="71" t="inlineStr">
+        <is>
+          <t>Cisterna 18 (OL180)</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="n">
+        <v>58420.5</v>
+      </c>
+      <c r="D16" s="71" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -2000,13 +3274,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C12"/>
+  <dimension ref="B2:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -2014,97 +3288,108 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="49" t="inlineStr">
-        <is>
-          <t>KPIs (referencia)</t>
+      <c r="B2" s="72" t="inlineStr">
+        <is>
+          <t>KPIs (referencia tecnica)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="50" t="inlineStr">
+      <c r="B5" s="73" t="inlineStr">
         <is>
           <t>Total Ingresos</t>
         </is>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="74">
         <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="50" t="inlineStr">
+      <c r="B6" s="73" t="inlineStr">
         <is>
           <t>Total Gastos</t>
         </is>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="74">
         <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="50" t="inlineStr">
+      <c r="B7" s="73" t="inlineStr">
         <is>
           <t>Flujo Neto</t>
         </is>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="74">
         <f>C5-C6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="50" t="inlineStr">
+      <c r="B8" s="73" t="inlineStr">
         <is>
           <t># Cobros</t>
         </is>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="75">
         <f>COUNTIFS(Transacciones!E:E,"in")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="50" t="inlineStr">
+      <c r="B9" s="73" t="inlineStr">
         <is>
           <t># Pagos</t>
         </is>
       </c>
-      <c r="C9" s="52">
+      <c r="C9" s="75">
         <f>COUNTIFS(Transacciones!E:E,"out")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="50" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>Banco (calculado)</t>
         </is>
       </c>
-      <c r="C10" s="51">
-        <f>Portada!C10</f>
+      <c r="C10" s="74">
+        <f>Portada!C12</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="50" t="inlineStr">
+      <c r="B11" s="73" t="inlineStr">
         <is>
           <t>Gandolas (calculado)</t>
         </is>
       </c>
-      <c r="C11" s="51">
-        <f>Portada!E10</f>
+      <c r="C11" s="74">
+        <f>Portada!E12</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="73" t="inlineStr">
         <is>
           <t>Por Cobrar (calculado)</t>
         </is>
       </c>
-      <c r="C12" s="51">
-        <f>Portada!G10</f>
+      <c r="C12" s="74">
+        <f>Portada!G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="73" t="inlineStr">
+        <is>
+          <t>Total Trazado</t>
+        </is>
+      </c>
+      <c r="C13" s="74">
+        <f>Portada!B8</f>
         <v/>
       </c>
     </row>

--- a/posts/demo-sheet-for-loom.xlsx
+++ b/posts/demo-sheet-for-loom.xlsx
@@ -567,158 +567,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Cashflow diario · Saldo acumulado</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Cashflow'!E5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Cashflow'!$B$6:$B$22</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cashflow'!$E$6:$E$22</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Cashflow'!F5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Cashflow'!$B$6:$B$22</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Cashflow'!$F$6:$F$22</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Fecha</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-        <tickLblSkip val="2"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Monto USD</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -785,22 +633,25 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="3960000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
+    <ext cx="7810500" cy="3333750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
     <clientData/>
   </oneCellAnchor>
 </wsDr>
@@ -1120,7 +971,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>REPOSITORIO ZELLE  ·  CONTROL FINANCIERO 360</t>
+          <t>REPOSITORIO DE PAGOS Y COBROS  ·  CONTROL FINANCIERO 360</t>
         </is>
       </c>
     </row>

--- a/posts/demo-sheet-for-loom.xlsx
+++ b/posts/demo-sheet-for-loom.xlsx
@@ -21,13 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0&quot; gandolas&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; cobros&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\%"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;[Red]-&quot;$&quot;#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.00\%"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00;[Red]-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,7 +79,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="000070C0"/>
       <sz val="11"/>
     </font>
     <font>
@@ -86,7 +89,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4D2E"/>
+      <color rgb="001A1A1A"/>
       <sz val="36"/>
     </font>
     <font>
@@ -101,7 +104,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4D2E"/>
+      <color rgb="0000B050"/>
       <sz val="20"/>
     </font>
     <font>
@@ -111,7 +114,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00059669"/>
+      <color rgb="001A1A1A"/>
       <sz val="20"/>
     </font>
     <font>
@@ -156,26 +159,27 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002563EB"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00166534"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="00991B1B"/>
+      <color rgb="000070C0"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4D2E"/>
-      <sz val="11"/>
+      <color rgb="0000B050"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00991B1B"/>
-      <sz val="11"/>
+      <color rgb="00C9A961"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="0000B050"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -184,16 +188,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00059669"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4D2E"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00059669"/>
+      <color rgb="0000B050"/>
       <sz val="11"/>
     </font>
     <font>
@@ -201,25 +200,45 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="002563EB"/>
+      <color rgb="000070C0"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4D2E"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <color rgb="001A1A1A"/>
-      <sz val="11"/>
+      <color rgb="00C9A961"/>
+      <sz val="20"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002563EB"/>
-      <sz val="12"/>
+      <color rgb="0000B050"/>
+      <sz val="40"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4D2E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000B050"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <color rgb="0064748B"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -266,6 +285,31 @@
         <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B6914"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9A961"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -293,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -353,34 +397,34 @@
     <xf numFmtId="164" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,18 +497,46 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="29" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -472,25 +544,92 @@
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="36" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="38" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -631,12 +770,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7810500" cy="3333750"/>
+    <ext cx="9334500" cy="3619500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2883,19 +3022,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J23"/>
+  <dimension ref="B2:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="2" ht="38" customHeight="1">
@@ -2908,464 +3057,437 @@
     <row r="3">
       <c r="B3" s="56" t="inlineStr">
         <is>
-          <t>Movimientos consolidados por fecha. Ingresos / Gastos / Flujo / Saldo acumulado.</t>
-        </is>
-      </c>
-      <c r="I3" s="57" t="inlineStr">
+          <t>Movimientos consolidados por fecha. Filas: Ingresos / Gastos / Flujo Neto / Saldo Acumulado.</t>
+        </is>
+      </c>
+      <c r="R3" s="57" t="inlineStr">
         <is>
           <t>Saldo inicial (Dashboard!E5):</t>
         </is>
       </c>
-      <c r="J3" s="58">
+      <c r="U3" s="58">
         <f>Dashboard!E5</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Ingresos</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Gastos</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Flujo Neto</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Saldo Acumulado</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="C6" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-18")</f>
-        <v/>
-      </c>
-      <c r="D6" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-18")</f>
-        <v/>
-      </c>
-      <c r="E6" s="61">
-        <f>C6-D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="58">
-        <f>$J$3+E6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="C7" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-19")</f>
-        <v/>
-      </c>
-      <c r="D7" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-19")</f>
-        <v/>
-      </c>
-      <c r="E7" s="61">
-        <f>C7-D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="58">
-        <f>F6+E7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C8" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-20")</f>
-        <v/>
-      </c>
-      <c r="D8" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-20")</f>
-        <v/>
-      </c>
-      <c r="E8" s="61">
-        <f>C8-D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="58">
-        <f>F7+E8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C9" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-21")</f>
-        <v/>
-      </c>
-      <c r="D9" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-21")</f>
-        <v/>
-      </c>
-      <c r="E9" s="61">
-        <f>C9-D9</f>
-        <v/>
-      </c>
-      <c r="F9" s="58">
-        <f>F8+E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C10" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-22")</f>
-        <v/>
-      </c>
-      <c r="D10" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-22")</f>
-        <v/>
-      </c>
-      <c r="E10" s="61">
-        <f>C10-D10</f>
-        <v/>
-      </c>
-      <c r="F10" s="58">
-        <f>F9+E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C11" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-23")</f>
-        <v/>
-      </c>
-      <c r="D11" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-23")</f>
-        <v/>
-      </c>
-      <c r="E11" s="61">
-        <f>C11-D11</f>
-        <v/>
-      </c>
-      <c r="F11" s="58">
-        <f>F10+E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C12" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-24")</f>
-        <v/>
-      </c>
-      <c r="D12" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-24")</f>
-        <v/>
-      </c>
-      <c r="E12" s="61">
-        <f>C12-D12</f>
-        <v/>
-      </c>
-      <c r="F12" s="58">
-        <f>F11+E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="C13" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-25")</f>
-        <v/>
-      </c>
-      <c r="D13" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-25")</f>
-        <v/>
-      </c>
-      <c r="E13" s="61">
-        <f>C13-D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="58">
-        <f>F12+E13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C14" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-26")</f>
-        <v/>
-      </c>
-      <c r="D14" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-26")</f>
-        <v/>
-      </c>
-      <c r="E14" s="61">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="58">
-        <f>F13+E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C15" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-27")</f>
-        <v/>
-      </c>
-      <c r="D15" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-27")</f>
-        <v/>
-      </c>
-      <c r="E15" s="61">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="58">
-        <f>F14+E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C16" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-28")</f>
-        <v/>
-      </c>
-      <c r="D16" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-28")</f>
-        <v/>
-      </c>
-      <c r="E16" s="61">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="58">
-        <f>F15+E16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C17" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-29")</f>
-        <v/>
-      </c>
-      <c r="D17" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-29")</f>
-        <v/>
-      </c>
-      <c r="E17" s="61">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="58">
-        <f>F16+E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="44" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C18" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-04-30")</f>
-        <v/>
-      </c>
-      <c r="D18" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-04-30")</f>
-        <v/>
-      </c>
-      <c r="E18" s="61">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="58">
-        <f>F17+E18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="44" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C19" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-05-01")</f>
-        <v/>
-      </c>
-      <c r="D19" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-05-01")</f>
-        <v/>
-      </c>
-      <c r="E19" s="61">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="58">
-        <f>F18+E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="44" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="C20" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-05-02")</f>
-        <v/>
-      </c>
-      <c r="D20" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-05-02")</f>
-        <v/>
-      </c>
-      <c r="E20" s="61">
-        <f>C20-D20</f>
-        <v/>
-      </c>
-      <c r="F20" s="58">
-        <f>F19+E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="C21" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-05-03")</f>
-        <v/>
-      </c>
-      <c r="D21" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-05-03")</f>
-        <v/>
-      </c>
-      <c r="E21" s="61">
-        <f>C21-D21</f>
-        <v/>
-      </c>
-      <c r="F21" s="58">
-        <f>F20+E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="44" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C22" s="59">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in",Transacciones!B:B,"2026-05-04")</f>
-        <v/>
-      </c>
-      <c r="D22" s="60">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out",Transacciones!B:B,"2026-05-04")</f>
-        <v/>
-      </c>
-      <c r="E22" s="61">
-        <f>C22-D22</f>
-        <v/>
-      </c>
-      <c r="F22" s="58">
-        <f>F21+E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="62" t="inlineStr">
-        <is>
-          <t>TOTAL PERIODO</t>
-        </is>
-      </c>
-      <c r="C23" s="63">
-        <f>SUM(C6:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="64">
-        <f>SUM(D6:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="65">
-        <f>C23-D23</f>
-        <v/>
-      </c>
-      <c r="F23" s="66">
-        <f>F22</f>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C5" s="59" t="inlineStr">
+        <is>
+          <t>18-Apr</t>
+        </is>
+      </c>
+      <c r="D5" s="59" t="inlineStr">
+        <is>
+          <t>19-Apr</t>
+        </is>
+      </c>
+      <c r="E5" s="59" t="inlineStr">
+        <is>
+          <t>20-Apr</t>
+        </is>
+      </c>
+      <c r="F5" s="59" t="inlineStr">
+        <is>
+          <t>21-Apr</t>
+        </is>
+      </c>
+      <c r="G5" s="59" t="inlineStr">
+        <is>
+          <t>22-Apr</t>
+        </is>
+      </c>
+      <c r="H5" s="59" t="inlineStr">
+        <is>
+          <t>23-Apr</t>
+        </is>
+      </c>
+      <c r="I5" s="59" t="inlineStr">
+        <is>
+          <t>24-Apr</t>
+        </is>
+      </c>
+      <c r="J5" s="59" t="inlineStr">
+        <is>
+          <t>25-Apr</t>
+        </is>
+      </c>
+      <c r="K5" s="59" t="inlineStr">
+        <is>
+          <t>26-Apr</t>
+        </is>
+      </c>
+      <c r="L5" s="59" t="inlineStr">
+        <is>
+          <t>27-Apr</t>
+        </is>
+      </c>
+      <c r="M5" s="59" t="inlineStr">
+        <is>
+          <t>28-Apr</t>
+        </is>
+      </c>
+      <c r="N5" s="59" t="inlineStr">
+        <is>
+          <t>29-Apr</t>
+        </is>
+      </c>
+      <c r="O5" s="59" t="inlineStr">
+        <is>
+          <t>30-Apr</t>
+        </is>
+      </c>
+      <c r="P5" s="59" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
+      <c r="Q5" s="59" t="inlineStr">
+        <is>
+          <t>02-May</t>
+        </is>
+      </c>
+      <c r="R5" s="59" t="inlineStr">
+        <is>
+          <t>03-May</t>
+        </is>
+      </c>
+      <c r="S5" s="59" t="inlineStr">
+        <is>
+          <t>04-May</t>
+        </is>
+      </c>
+      <c r="T5" s="60" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>INGRESOS</t>
+        </is>
+      </c>
+      <c r="C6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-18")</f>
+        <v/>
+      </c>
+      <c r="D6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-19")</f>
+        <v/>
+      </c>
+      <c r="E6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-20")</f>
+        <v/>
+      </c>
+      <c r="F6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-21")</f>
+        <v/>
+      </c>
+      <c r="G6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-22")</f>
+        <v/>
+      </c>
+      <c r="H6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-23")</f>
+        <v/>
+      </c>
+      <c r="I6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-24")</f>
+        <v/>
+      </c>
+      <c r="J6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-25")</f>
+        <v/>
+      </c>
+      <c r="K6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-26")</f>
+        <v/>
+      </c>
+      <c r="L6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-27")</f>
+        <v/>
+      </c>
+      <c r="M6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-28")</f>
+        <v/>
+      </c>
+      <c r="N6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-29")</f>
+        <v/>
+      </c>
+      <c r="O6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-04-30")</f>
+        <v/>
+      </c>
+      <c r="P6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-05-01")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-05-02")</f>
+        <v/>
+      </c>
+      <c r="R6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-05-03")</f>
+        <v/>
+      </c>
+      <c r="S6" s="62">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"in",Transacciones!$B:$B,"2026-05-04")</f>
+        <v/>
+      </c>
+      <c r="T6" s="63">
+        <f>SUM(C6:S6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>GASTOS</t>
+        </is>
+      </c>
+      <c r="C7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-18")</f>
+        <v/>
+      </c>
+      <c r="D7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-19")</f>
+        <v/>
+      </c>
+      <c r="E7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-20")</f>
+        <v/>
+      </c>
+      <c r="F7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-21")</f>
+        <v/>
+      </c>
+      <c r="G7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-22")</f>
+        <v/>
+      </c>
+      <c r="H7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-23")</f>
+        <v/>
+      </c>
+      <c r="I7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-24")</f>
+        <v/>
+      </c>
+      <c r="J7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-25")</f>
+        <v/>
+      </c>
+      <c r="K7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-26")</f>
+        <v/>
+      </c>
+      <c r="L7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-27")</f>
+        <v/>
+      </c>
+      <c r="M7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-28")</f>
+        <v/>
+      </c>
+      <c r="N7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-29")</f>
+        <v/>
+      </c>
+      <c r="O7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-04-30")</f>
+        <v/>
+      </c>
+      <c r="P7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-05-01")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-05-02")</f>
+        <v/>
+      </c>
+      <c r="R7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-05-03")</f>
+        <v/>
+      </c>
+      <c r="S7" s="65">
+        <f>SUMIFS(Transacciones!$D:$D,Transacciones!$E:$E,"out",Transacciones!$B:$B,"2026-05-04")</f>
+        <v/>
+      </c>
+      <c r="T7" s="63">
+        <f>SUM(C7:S7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="66" t="inlineStr">
+        <is>
+          <t>FLUJO NETO</t>
+        </is>
+      </c>
+      <c r="C8" s="67">
+        <f>C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="67">
+        <f>D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="67">
+        <f>E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="67">
+        <f>F6-F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="67">
+        <f>G6-G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="67">
+        <f>H6-H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="67">
+        <f>I6-I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="67">
+        <f>J6-J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="67">
+        <f>K6-K7</f>
+        <v/>
+      </c>
+      <c r="L8" s="67">
+        <f>L6-L7</f>
+        <v/>
+      </c>
+      <c r="M8" s="67">
+        <f>M6-M7</f>
+        <v/>
+      </c>
+      <c r="N8" s="67">
+        <f>N6-N7</f>
+        <v/>
+      </c>
+      <c r="O8" s="67">
+        <f>O6-O7</f>
+        <v/>
+      </c>
+      <c r="P8" s="67">
+        <f>P6-P7</f>
+        <v/>
+      </c>
+      <c r="Q8" s="67">
+        <f>Q6-Q7</f>
+        <v/>
+      </c>
+      <c r="R8" s="67">
+        <f>R6-R7</f>
+        <v/>
+      </c>
+      <c r="S8" s="67">
+        <f>S6-S7</f>
+        <v/>
+      </c>
+      <c r="T8" s="63">
+        <f>T6-T7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="68" t="inlineStr">
+        <is>
+          <t>SALDO ACUMULADO</t>
+        </is>
+      </c>
+      <c r="C9" s="69">
+        <f>$U$3+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="69">
+        <f>C9+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="69">
+        <f>D9+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="69">
+        <f>E9+F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="69">
+        <f>F9+G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="69">
+        <f>G9+H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="69">
+        <f>H9+I8</f>
+        <v/>
+      </c>
+      <c r="J9" s="69">
+        <f>I9+J8</f>
+        <v/>
+      </c>
+      <c r="K9" s="69">
+        <f>J9+K8</f>
+        <v/>
+      </c>
+      <c r="L9" s="69">
+        <f>K9+L8</f>
+        <v/>
+      </c>
+      <c r="M9" s="69">
+        <f>L9+M8</f>
+        <v/>
+      </c>
+      <c r="N9" s="69">
+        <f>M9+N8</f>
+        <v/>
+      </c>
+      <c r="O9" s="69">
+        <f>N9+O8</f>
+        <v/>
+      </c>
+      <c r="P9" s="69">
+        <f>O9+P8</f>
+        <v/>
+      </c>
+      <c r="Q9" s="69">
+        <f>P9+Q8</f>
+        <v/>
+      </c>
+      <c r="R9" s="69">
+        <f>Q9+R8</f>
+        <v/>
+      </c>
+      <c r="S9" s="69">
+        <f>R9+S8</f>
+        <v/>
+      </c>
+      <c r="T9" s="70">
+        <f>$U$3+T8</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B2:G2"/>
+  <mergeCells count="3">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="R3:T3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3398,7 +3520,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>DEUDAS  ·  Por cobrar / Por pagar</t>
         </is>
@@ -3477,130 +3599,130 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="68" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>Luis Mendoza</t>
         </is>
       </c>
-      <c r="B4" s="68" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>Por Pagar</t>
         </is>
       </c>
-      <c r="C4" s="69" t="n">
+      <c r="C4" s="73" t="n">
         <v>40000</v>
       </c>
-      <c r="D4" s="68" t="inlineStr">
+      <c r="D4" s="72" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n">
+      <c r="E4" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="68" t="n">
+      <c r="F4" s="72" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="71" t="n">
+      <c r="G4" s="75" t="n">
         <v>1600</v>
       </c>
-      <c r="H4" s="71" t="n">
+      <c r="H4" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="72" t="n">
+      <c r="I4" s="76" t="n">
         <v>40000</v>
       </c>
-      <c r="J4" s="68" t="inlineStr"/>
-      <c r="K4" s="68" t="inlineStr"/>
-      <c r="L4" s="68" t="inlineStr">
+      <c r="J4" s="72" t="inlineStr"/>
+      <c r="K4" s="72" t="inlineStr"/>
+      <c r="L4" s="72" t="inlineStr">
         <is>
           <t>Transferencia mensual</t>
         </is>
       </c>
-      <c r="M4" s="68" t="inlineStr">
+      <c r="M4" s="72" t="inlineStr">
         <is>
           <t>Sin vcto.</t>
         </is>
       </c>
-      <c r="N4" s="68" t="inlineStr">
+      <c r="N4" s="72" t="inlineStr">
         <is>
           <t>Prestamo dic 2025. Capital $40,000. Interes 4% mensual fijo $1,600. Solo se pagan intereses; capital intacto.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>Pedro Ramos</t>
         </is>
       </c>
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Por Pagar</t>
         </is>
       </c>
-      <c r="C5" s="69" t="n">
+      <c r="C5" s="73" t="n">
         <v>50000</v>
       </c>
-      <c r="D5" s="68" t="inlineStr">
+      <c r="D5" s="72" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="E5" s="70" t="n">
+      <c r="E5" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="68" t="n">
+      <c r="F5" s="72" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="71" t="n">
+      <c r="G5" s="75" t="n">
         <v>2500</v>
       </c>
-      <c r="H5" s="71" t="n">
+      <c r="H5" s="75" t="n">
         <v>5000</v>
       </c>
-      <c r="I5" s="72" t="n">
+      <c r="I5" s="76" t="n">
         <v>45000</v>
       </c>
-      <c r="J5" s="68" t="inlineStr"/>
-      <c r="K5" s="68" t="inlineStr"/>
-      <c r="L5" s="68" t="inlineStr">
+      <c r="J5" s="72" t="inlineStr"/>
+      <c r="K5" s="72" t="inlineStr"/>
+      <c r="L5" s="72" t="inlineStr">
         <is>
           <t>Transferencia mensual</t>
         </is>
       </c>
-      <c r="M5" s="68" t="inlineStr">
+      <c r="M5" s="72" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
       </c>
-      <c r="N5" s="68" t="inlineStr">
+      <c r="N5" s="72" t="inlineStr">
         <is>
           <t>Prestamo dic 2025. Capital $50K. Interes 5% mensual $2,500. Abono $5K capital el 29-abr-26. Saldo vivo $45K.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="73" t="inlineStr">
+      <c r="A10" s="77" t="inlineStr">
         <is>
           <t>TOTAL POR PAGAR</t>
         </is>
       </c>
-      <c r="C10" s="66" t="n">
+      <c r="C10" s="78" t="n">
         <v>90000</v>
       </c>
-      <c r="G10" s="74" t="n">
+      <c r="G10" s="79" t="n">
         <v>4100</v>
       </c>
-      <c r="H10" s="74" t="n">
+      <c r="H10" s="79" t="n">
         <v>5000</v>
       </c>
-      <c r="I10" s="75" t="n">
+      <c r="I10" s="80" t="n">
         <v>85000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="76" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>CREDITO ROTATIVO PROVEEDOR</t>
         </is>
@@ -3629,20 +3751,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="82" t="inlineStr">
         <is>
           <t>Olivar Andaluz S.L.</t>
         </is>
       </c>
-      <c r="B16" s="78" t="inlineStr">
+      <c r="B16" s="83" t="inlineStr">
         <is>
           <t>Cisterna 18 (OL180)</t>
         </is>
       </c>
-      <c r="C16" s="58" t="n">
+      <c r="C16" s="84" t="n">
         <v>58420.5</v>
       </c>
-      <c r="D16" s="78" t="inlineStr">
+      <c r="D16" s="83" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -3663,164 +3785,437 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C17"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="79" t="inlineStr">
-        <is>
-          <t>KPIs (referencia tecnica)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="80" t="inlineStr">
-        <is>
-          <t>Total Ingresos</t>
-        </is>
-      </c>
-      <c r="C5" s="81">
+    <row r="2" ht="44" customHeight="1">
+      <c r="B2" s="85" t="inlineStr">
+        <is>
+          <t>KPIs OPERATIVOS  ·  OLIVAR DEL SUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Mes en curso · Mayo 2026  ·  Datos vivos: cualquier captura nueva recalcula esta vista</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>FLUJO NETO DEL PERIODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="B6" s="86">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in")-SUMIFS(Transacciones!D:D,Transacciones!E:E,"out")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Ingresos cobrados − Gastos pagados</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>DESGLOSE DE INGRESOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="87" t="inlineStr">
+        <is>
+          <t>COBROS A CLIENTES</t>
+        </is>
+      </c>
+      <c r="D12" s="87" t="inlineStr">
+        <is>
+          <t>COBROS A CREDITO</t>
+        </is>
+      </c>
+      <c r="F12" s="87" t="inlineStr">
+        <is>
+          <t>RETORNO GANDOLAS</t>
+        </is>
+      </c>
+      <c r="H12" s="88" t="inlineStr">
+        <is>
+          <t>TOTAL INGRESOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="B13" s="89">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"cobro_cliente")</f>
+        <v/>
+      </c>
+      <c r="D13" s="89">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"cobro_credito")</f>
+        <v/>
+      </c>
+      <c r="F13" s="89">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"retorno_gandola")</f>
+        <v/>
+      </c>
+      <c r="H13" s="90">
         <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"in")</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="80" t="inlineStr">
-        <is>
-          <t>Total Gastos</t>
-        </is>
-      </c>
-      <c r="C6" s="81">
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="91" t="inlineStr">
+        <is>
+          <t>Categoria cobro_cliente</t>
+        </is>
+      </c>
+      <c r="D14" s="91" t="inlineStr">
+        <is>
+          <t>Categoria cobro_credito</t>
+        </is>
+      </c>
+      <c r="F14" s="91" t="inlineStr">
+        <is>
+          <t>Categoria retorno_gandola</t>
+        </is>
+      </c>
+      <c r="H14" s="92" t="inlineStr">
+        <is>
+          <t>Suma direccion in</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>DESGLOSE DE GASTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="93" t="inlineStr">
+        <is>
+          <t>PAGOS A PROVEEDORES</t>
+        </is>
+      </c>
+      <c r="D19" s="93" t="inlineStr">
+        <is>
+          <t>INTERES DE DEUDA</t>
+        </is>
+      </c>
+      <c r="F19" s="93" t="inlineStr">
+        <is>
+          <t>CAPITAL DE DEUDA</t>
+        </is>
+      </c>
+      <c r="H19" s="88" t="inlineStr">
+        <is>
+          <t>TOTAL GASTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="B20" s="94">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"pago_proveedor")</f>
+        <v/>
+      </c>
+      <c r="D20" s="94">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"pago_deuda_interes")</f>
+        <v/>
+      </c>
+      <c r="F20" s="94">
+        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"pago_deuda_capital")</f>
+        <v/>
+      </c>
+      <c r="H20" s="90">
         <f>SUMIFS(Transacciones!D:D,Transacciones!E:E,"out")</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="80" t="inlineStr">
-        <is>
-          <t>Pagos a Proveedores</t>
-        </is>
-      </c>
-      <c r="C7" s="81">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"pago_proveedor")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="80" t="inlineStr">
-        <is>
-          <t>Pagos Deuda Interes</t>
-        </is>
-      </c>
-      <c r="C8" s="81">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"pago_deuda_interes")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="80" t="inlineStr">
-        <is>
-          <t>Pagos Deuda Capital</t>
-        </is>
-      </c>
-      <c r="C9" s="81">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"pago_deuda_capital")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="80" t="inlineStr">
-        <is>
-          <t>Cobros Clientes</t>
-        </is>
-      </c>
-      <c r="C10" s="81">
-        <f>SUMIFS(Transacciones!D:D,Transacciones!F:F,"cobro_cliente")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="80" t="inlineStr">
-        <is>
-          <t>Flujo Neto</t>
-        </is>
-      </c>
-      <c r="C11" s="81">
-        <f>C5-C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="80" t="inlineStr">
-        <is>
-          <t># Cobros</t>
-        </is>
-      </c>
-      <c r="C12" s="82">
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="95" t="inlineStr">
+        <is>
+          <t>Categoria pago_proveedor</t>
+        </is>
+      </c>
+      <c r="D21" s="95" t="inlineStr">
+        <is>
+          <t>Categoria pago_deuda_interes</t>
+        </is>
+      </c>
+      <c r="F21" s="95" t="inlineStr">
+        <is>
+          <t>Abonos a principal</t>
+        </is>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>Suma direccion out</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>OPERACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="96" t="inlineStr">
+        <is>
+          <t># COBROS RECIBIDOS</t>
+        </is>
+      </c>
+      <c r="D26" s="96" t="inlineStr">
+        <is>
+          <t># PAGOS REALIZADOS</t>
+        </is>
+      </c>
+      <c r="F26" s="96" t="inlineStr">
+        <is>
+          <t>TICKET PROMEDIO COBRO</t>
+        </is>
+      </c>
+      <c r="H26" s="96" t="inlineStr">
+        <is>
+          <t>TICKET PROMEDIO GASTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="B27" s="97">
         <f>COUNTIFS(Transacciones!E:E,"in")</f>
         <v/>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="80" t="inlineStr">
-        <is>
-          <t># Pagos</t>
-        </is>
-      </c>
-      <c r="C13" s="82">
+      <c r="D27" s="97">
         <f>COUNTIFS(Transacciones!E:E,"out")</f>
         <v/>
       </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="80" t="inlineStr">
-        <is>
-          <t>Banco (calculado)</t>
-        </is>
-      </c>
-      <c r="C14" s="81">
+      <c r="F27" s="98">
+        <f>IFERROR(SUMIFS(Transacciones!D:D,Transacciones!E:E,"in")/COUNTIFS(Transacciones!E:E,"in"),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="98">
+        <f>IFERROR(SUMIFS(Transacciones!D:D,Transacciones!E:E,"out")/COUNTIFS(Transacciones!E:E,"out"),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="99" t="inlineStr">
+        <is>
+          <t>Capturas entrantes</t>
+        </is>
+      </c>
+      <c r="D28" s="99" t="inlineStr">
+        <is>
+          <t>Salidas de caja</t>
+        </is>
+      </c>
+      <c r="F28" s="99" t="inlineStr">
+        <is>
+          <t>Promedio por captura</t>
+        </is>
+      </c>
+      <c r="H28" s="99" t="inlineStr">
+        <is>
+          <t>Promedio salida</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>POSICION DE EFECTIVO  (link Dashboard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="B33" s="96" t="inlineStr">
+        <is>
+          <t>EFECTIVO EN BANCO</t>
+        </is>
+      </c>
+      <c r="D33" s="100" t="inlineStr">
+        <is>
+          <t>CAPITAL EN GANDOLAS</t>
+        </is>
+      </c>
+      <c r="F33" s="101" t="inlineStr">
+        <is>
+          <t>CUENTAS POR COBRAR</t>
+        </is>
+      </c>
+      <c r="H33" s="88" t="inlineStr">
+        <is>
+          <t>TOTAL TRAZADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="B34" s="102">
         <f>Dashboard!C12</f>
         <v/>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="80" t="inlineStr">
-        <is>
-          <t>Gandolas (calculado)</t>
-        </is>
-      </c>
-      <c r="C15" s="81">
+      <c r="D34" s="103">
         <f>Dashboard!E12</f>
         <v/>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="80" t="inlineStr">
-        <is>
-          <t>Por Cobrar (calculado)</t>
-        </is>
-      </c>
-      <c r="C16" s="81">
+      <c r="F34" s="104">
         <f>Dashboard!G12</f>
         <v/>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="80" t="inlineStr">
-        <is>
-          <t>Total Trazado</t>
-        </is>
-      </c>
-      <c r="C17" s="81">
+      <c r="H34" s="90">
         <f>Dashboard!B8</f>
         <v/>
       </c>
     </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="99" t="inlineStr">
+        <is>
+          <t>Saldo liquido</t>
+        </is>
+      </c>
+      <c r="D35" s="105" t="inlineStr">
+        <is>
+          <t>En transito</t>
+        </is>
+      </c>
+      <c r="F35" s="106" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>Suma 3 buckets</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="107" t="inlineStr">
+        <is>
+          <t>Convencion de colores (estandar finance / IB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="82" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="C39" s="108" t="inlineStr">
+        <is>
+          <t>input hardcodeado (saldo inicial, datos de transaccion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="C40" s="108" t="inlineStr">
+        <is>
+          <t>formula que opera sobre celdas de la misma pestaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="109" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="C41" s="108" t="inlineStr">
+        <is>
+          <t>formula que referencia OTRA pestaña (link cross-sheet)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="61">
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="C40:I40"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="H26:I26"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>